--- a/ds/3des/03-pdm1/aula02/juros-compostos.xlsx
+++ b/ds/3des/03-pdm1/aula02/juros-compostos.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\wellington\senai2025\ds\3des\03-pdm1\aula02\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\wellington\senai2025\ds\3des\03-pdm1\aula02\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF5B7275-3259-492D-B5A0-C4475FF5F1DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E54D9F4-26B9-4A03-A2E3-F3DE9E69C0B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{C6C0B6A0-96AC-40D2-A26A-C7C96E3D3892}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C6C0B6A0-96AC-40D2-A26A-C7C96E3D3892}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="14">
   <si>
     <t>meses</t>
   </si>
@@ -67,13 +67,26 @@
   <si>
     <t>Tempo total de meses</t>
   </si>
+  <si>
+    <t>Mil reais rendendo juros por 10 anos</t>
+  </si>
+  <si>
+    <t>Mil reais todo mês por 10 anos</t>
+  </si>
+  <si>
+    <t>Total sem juros</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> =K10*(1+K11)^K12</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="44" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -108,18 +121,30 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="Moeda" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Vírgula" xfId="2" builtinId="3"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -451,2508 +476,2526 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2AE5787A-7910-47D4-B79F-E1F6CCE11091}">
-  <dimension ref="A1:J122"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:K122"/>
+  <sheetFormatPr defaultColWidth="13.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="5" max="5" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="4.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="13.85546875" style="2"/>
+    <col min="5" max="5" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.85546875" style="3"/>
+    <col min="9" max="9" width="7.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="F1" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1" s="6"/>
+      <c r="H1" s="6"/>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>0</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="2">
         <v>1000</v>
       </c>
-      <c r="D2">
+      <c r="E2" s="5">
         <v>1000</v>
       </c>
-      <c r="E2" s="2">
+      <c r="F2" s="3">
         <v>0</v>
       </c>
-      <c r="F2" s="2">
-        <f>$D$2</f>
+      <c r="G2" s="2">
+        <f>$E$2</f>
         <v>1000</v>
       </c>
-      <c r="G2" s="2">
-        <f>F2*$D$3</f>
+      <c r="H2" s="2">
+        <f>G2*$E$3</f>
         <v>10</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>1</v>
       </c>
-      <c r="B3">
-        <f>B2+B2*$D$3</f>
+      <c r="B3" s="2">
+        <f>B2+B2*$E$3</f>
         <v>1010</v>
       </c>
-      <c r="D3" s="1">
+      <c r="E3" s="1">
         <v>0.01</v>
       </c>
-      <c r="E3" s="2">
+      <c r="F3" s="3">
         <v>1</v>
       </c>
-      <c r="F3" s="2">
-        <f>F2+G2+$D$2</f>
+      <c r="G3" s="2">
+        <f>G2+H2+$E$2</f>
         <v>2010</v>
       </c>
-      <c r="G3" s="2">
-        <f>F3*$D$3</f>
+      <c r="H3" s="2">
+        <f>G3*$E$3</f>
         <v>20.100000000000001</v>
       </c>
-      <c r="I3" t="s">
+      <c r="J3" t="s">
         <v>2</v>
       </c>
-      <c r="J3" t="s">
+      <c r="K3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>2</v>
       </c>
-      <c r="B4">
-        <f t="shared" ref="B4:B67" si="0">B3+B3*$D$3</f>
+      <c r="B4" s="2">
+        <f t="shared" ref="B4:B67" si="0">B3+B3*$E$3</f>
         <v>1020.1</v>
       </c>
-      <c r="E4" s="2">
+      <c r="D4">
+        <v>120</v>
+      </c>
+      <c r="E4" t="s">
+        <v>0</v>
+      </c>
+      <c r="F4" s="3">
         <v>2</v>
       </c>
-      <c r="F4" s="2">
-        <f t="shared" ref="F4:F11" si="1">F3+G3+$D$2</f>
+      <c r="G4" s="2">
+        <f t="shared" ref="G4:G11" si="1">G3+H3+$E$2</f>
         <v>3030.1</v>
       </c>
-      <c r="G4" s="2">
-        <f t="shared" ref="G4:G67" si="2">F4*$D$3</f>
+      <c r="H4" s="2">
+        <f t="shared" ref="H4:H67" si="2">G4*$E$3</f>
         <v>30.300999999999998</v>
       </c>
-      <c r="I4" t="s">
+      <c r="J4" t="s">
         <v>4</v>
       </c>
-      <c r="J4" t="s">
+      <c r="K4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>3</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="2">
         <f t="shared" si="0"/>
         <v>1030.3009999999999</v>
       </c>
-      <c r="C5">
-        <v>120</v>
-      </c>
       <c r="D5" t="s">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E5" s="2">
+        <f>D4*E2</f>
+        <v>120000</v>
+      </c>
+      <c r="F5" s="3">
         <v>3</v>
       </c>
-      <c r="F5" s="2">
+      <c r="G5" s="2">
         <f t="shared" si="1"/>
         <v>4060.4009999999998</v>
       </c>
-      <c r="G5" s="2">
+      <c r="H5" s="2">
         <f t="shared" si="2"/>
         <v>40.604010000000002</v>
       </c>
-      <c r="I5" t="s">
+      <c r="J5" t="s">
         <v>6</v>
       </c>
-      <c r="J5" t="s">
+      <c r="K5" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>4</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="2">
         <f t="shared" si="0"/>
         <v>1040.60401</v>
       </c>
-      <c r="C6">
-        <f>C5*D2</f>
-        <v>120000</v>
-      </c>
-      <c r="E6" s="2">
+      <c r="F6" s="3">
         <v>4</v>
       </c>
-      <c r="F6" s="2">
+      <c r="G6" s="2">
         <f t="shared" si="1"/>
         <v>5101.0050099999999</v>
       </c>
-      <c r="G6" s="2">
+      <c r="H6" s="2">
         <f t="shared" si="2"/>
         <v>51.010050100000001</v>
       </c>
-      <c r="I6" t="s">
+      <c r="J6" t="s">
         <v>8</v>
       </c>
-      <c r="J6" t="s">
+      <c r="K6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>5</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="2">
         <f t="shared" si="0"/>
         <v>1051.0100500999999</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="3">
         <v>5</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <f t="shared" si="1"/>
         <v>6152.0150600999996</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <f t="shared" si="2"/>
         <v>61.520150600999997</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>6</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="2">
         <f t="shared" si="0"/>
         <v>1061.5201506009998</v>
       </c>
-      <c r="E8" s="2">
+      <c r="F8" s="3">
         <v>6</v>
       </c>
-      <c r="F8" s="2">
+      <c r="G8" s="2">
         <f t="shared" si="1"/>
         <v>7213.5352107009994</v>
       </c>
-      <c r="G8" s="2">
+      <c r="H8" s="2">
         <f t="shared" si="2"/>
         <v>72.135352107009993</v>
       </c>
-      <c r="I8" t="s">
-        <v>2</v>
-      </c>
-      <c r="J8" s="2">
-        <f>J9*(1+J10)^J11</f>
-        <v>3300.3868945736699</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>7</v>
       </c>
-      <c r="B9">
+      <c r="B9" s="2">
         <f t="shared" si="0"/>
         <v>1072.1353521070098</v>
       </c>
-      <c r="E9" s="2">
+      <c r="F9" s="3">
         <v>7</v>
       </c>
-      <c r="F9" s="2">
+      <c r="G9" s="2">
         <f t="shared" si="1"/>
         <v>8285.670562808009</v>
       </c>
-      <c r="G9" s="2">
+      <c r="H9" s="2">
         <f t="shared" si="2"/>
         <v>82.856705628080093</v>
       </c>
-      <c r="I9" t="s">
-        <v>4</v>
-      </c>
-      <c r="J9">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J9" t="s">
+        <v>2</v>
+      </c>
+      <c r="K9" s="2">
+        <f>K10*(1+K11)^K12</f>
+        <v>3300.3868945736699</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>8</v>
       </c>
-      <c r="B10">
+      <c r="B10" s="2">
         <f t="shared" si="0"/>
         <v>1082.8567056280799</v>
       </c>
-      <c r="E10" s="2">
+      <c r="F10" s="3">
         <v>8</v>
       </c>
-      <c r="F10" s="2">
+      <c r="G10" s="2">
         <f t="shared" si="1"/>
         <v>9368.5272684360898</v>
       </c>
-      <c r="G10" s="2">
+      <c r="H10" s="2">
         <f t="shared" si="2"/>
         <v>93.685272684360896</v>
       </c>
-      <c r="I10" t="s">
-        <v>6</v>
-      </c>
-      <c r="J10" s="1">
-        <v>0.01</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J10" t="s">
+        <v>4</v>
+      </c>
+      <c r="K10" s="2">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>9</v>
       </c>
-      <c r="B11">
+      <c r="B11" s="2">
         <f t="shared" si="0"/>
         <v>1093.6852726843606</v>
       </c>
-      <c r="E11" s="2">
+      <c r="F11" s="3">
         <v>9</v>
       </c>
-      <c r="F11" s="2">
+      <c r="G11" s="2">
         <f t="shared" si="1"/>
         <v>10462.212541120451</v>
       </c>
-      <c r="G11" s="2">
+      <c r="H11" s="2">
         <f t="shared" si="2"/>
         <v>104.62212541120451</v>
       </c>
-      <c r="I11" t="s">
-        <v>8</v>
-      </c>
-      <c r="J11">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J11" t="s">
+        <v>6</v>
+      </c>
+      <c r="K11" s="1">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>10</v>
       </c>
-      <c r="B12">
+      <c r="B12" s="2">
         <f t="shared" si="0"/>
         <v>1104.6221254112043</v>
       </c>
-      <c r="E12" s="2">
+      <c r="F12" s="3">
         <v>10</v>
       </c>
-      <c r="F12" s="2">
-        <f t="shared" ref="F12:F75" si="3">F11+G11+$D$2</f>
+      <c r="G12" s="2">
+        <f t="shared" ref="G12:G75" si="3">G11+H11+$E$2</f>
         <v>11566.834666531655</v>
       </c>
-      <c r="G12" s="2">
+      <c r="H12" s="2">
         <f t="shared" si="2"/>
         <v>115.66834666531655</v>
       </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J12" t="s">
+        <v>8</v>
+      </c>
+      <c r="K12">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>11</v>
       </c>
-      <c r="B13">
+      <c r="B13" s="2">
         <f t="shared" si="0"/>
         <v>1115.6683466653162</v>
       </c>
-      <c r="E13" s="2">
+      <c r="F13" s="3">
         <v>11</v>
       </c>
-      <c r="F13" s="2">
+      <c r="G13" s="2">
         <f t="shared" si="3"/>
         <v>12682.503013196971</v>
       </c>
-      <c r="G13" s="2">
+      <c r="H13" s="2">
         <f t="shared" si="2"/>
         <v>126.82503013196971</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>12</v>
       </c>
-      <c r="B14">
+      <c r="B14" s="2">
         <f t="shared" si="0"/>
         <v>1126.8250301319695</v>
       </c>
-      <c r="E14" s="2">
+      <c r="F14" s="3">
         <v>12</v>
       </c>
-      <c r="F14" s="2">
+      <c r="G14" s="2">
         <f t="shared" si="3"/>
         <v>13809.32804332894</v>
       </c>
-      <c r="G14" s="2">
+      <c r="H14" s="2">
         <f t="shared" si="2"/>
         <v>138.09328043328941</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>13</v>
       </c>
-      <c r="B15">
+      <c r="B15" s="2">
         <f t="shared" si="0"/>
         <v>1138.0932804332892</v>
       </c>
-      <c r="E15" s="2">
+      <c r="F15" s="3">
         <v>13</v>
       </c>
-      <c r="F15" s="2">
+      <c r="G15" s="2">
         <f t="shared" si="3"/>
         <v>14947.42132376223</v>
       </c>
-      <c r="G15" s="2">
+      <c r="H15" s="2">
         <f t="shared" si="2"/>
         <v>149.47421323762231</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>14</v>
       </c>
-      <c r="B16">
+      <c r="B16" s="2">
         <f t="shared" si="0"/>
         <v>1149.4742132376221</v>
       </c>
-      <c r="E16" s="2">
+      <c r="F16" s="3">
         <v>14</v>
       </c>
-      <c r="F16" s="2">
+      <c r="G16" s="2">
         <f t="shared" si="3"/>
         <v>16096.895536999853</v>
       </c>
-      <c r="G16" s="2">
+      <c r="H16" s="2">
         <f t="shared" si="2"/>
         <v>160.96895536999853</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>15</v>
       </c>
-      <c r="B17">
+      <c r="B17" s="2">
         <f t="shared" si="0"/>
         <v>1160.9689553699982</v>
       </c>
-      <c r="E17" s="2">
+      <c r="F17" s="3">
         <v>15</v>
       </c>
-      <c r="F17" s="2">
+      <c r="G17" s="2">
         <f t="shared" si="3"/>
         <v>17257.864492369852</v>
       </c>
-      <c r="G17" s="2">
+      <c r="H17" s="2">
         <f t="shared" si="2"/>
         <v>172.57864492369853</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>16</v>
       </c>
-      <c r="B18">
+      <c r="B18" s="2">
         <f t="shared" si="0"/>
         <v>1172.5786449236982</v>
       </c>
-      <c r="E18" s="2">
+      <c r="F18" s="3">
         <v>16</v>
       </c>
-      <c r="F18" s="2">
+      <c r="G18" s="2">
         <f t="shared" si="3"/>
         <v>18430.443137293551</v>
       </c>
-      <c r="G18" s="2">
+      <c r="H18" s="2">
         <f t="shared" si="2"/>
         <v>184.30443137293551</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>17</v>
       </c>
-      <c r="B19">
+      <c r="B19" s="2">
         <f t="shared" si="0"/>
         <v>1184.3044313729351</v>
       </c>
-      <c r="E19" s="2">
+      <c r="F19" s="3">
         <v>17</v>
       </c>
-      <c r="F19" s="2">
+      <c r="G19" s="2">
         <f t="shared" si="3"/>
         <v>19614.747568666487</v>
       </c>
-      <c r="G19" s="2">
+      <c r="H19" s="2">
         <f t="shared" si="2"/>
         <v>196.14747568666488</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>18</v>
       </c>
-      <c r="B20">
+      <c r="B20" s="2">
         <f t="shared" si="0"/>
         <v>1196.1474756866644</v>
       </c>
-      <c r="E20" s="2">
+      <c r="F20" s="3">
         <v>18</v>
       </c>
-      <c r="F20" s="2">
+      <c r="G20" s="2">
         <f t="shared" si="3"/>
         <v>20810.895044353154</v>
       </c>
-      <c r="G20" s="2">
+      <c r="H20" s="2">
         <f t="shared" si="2"/>
         <v>208.10895044353154</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>19</v>
       </c>
-      <c r="B21">
+      <c r="B21" s="2">
         <f t="shared" si="0"/>
         <v>1208.1089504435311</v>
       </c>
-      <c r="E21" s="2">
+      <c r="F21" s="3">
         <v>19</v>
       </c>
-      <c r="F21" s="2">
+      <c r="G21" s="2">
         <f t="shared" si="3"/>
         <v>22019.003994796687</v>
       </c>
-      <c r="G21" s="2">
+      <c r="H21" s="2">
         <f t="shared" si="2"/>
         <v>220.19003994796688</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>20</v>
       </c>
-      <c r="B22">
+      <c r="B22" s="2">
         <f t="shared" si="0"/>
         <v>1220.1900399479664</v>
       </c>
-      <c r="E22" s="2">
+      <c r="F22" s="3">
         <v>20</v>
       </c>
-      <c r="F22" s="2">
+      <c r="G22" s="2">
         <f t="shared" si="3"/>
         <v>23239.194034744654</v>
       </c>
-      <c r="G22" s="2">
+      <c r="H22" s="2">
         <f t="shared" si="2"/>
         <v>232.39194034744654</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>21</v>
       </c>
-      <c r="B23">
+      <c r="B23" s="2">
         <f t="shared" si="0"/>
         <v>1232.3919403474461</v>
       </c>
-      <c r="E23" s="2">
+      <c r="F23" s="3">
         <v>21</v>
       </c>
-      <c r="F23" s="2">
+      <c r="G23" s="2">
         <f t="shared" si="3"/>
         <v>24471.585975092101</v>
       </c>
-      <c r="G23" s="2">
+      <c r="H23" s="2">
         <f t="shared" si="2"/>
         <v>244.71585975092103</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>22</v>
       </c>
-      <c r="B24">
+      <c r="B24" s="2">
         <f t="shared" si="0"/>
         <v>1244.7158597509206</v>
       </c>
-      <c r="E24" s="2">
+      <c r="F24" s="3">
         <v>22</v>
       </c>
-      <c r="F24" s="2">
+      <c r="G24" s="2">
         <f t="shared" si="3"/>
         <v>25716.301834843023</v>
       </c>
-      <c r="G24" s="2">
+      <c r="H24" s="2">
         <f t="shared" si="2"/>
         <v>257.16301834843023</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>23</v>
       </c>
-      <c r="B25">
+      <c r="B25" s="2">
         <f t="shared" si="0"/>
         <v>1257.1630183484299</v>
       </c>
-      <c r="E25" s="2">
+      <c r="F25" s="3">
         <v>23</v>
       </c>
-      <c r="F25" s="2">
+      <c r="G25" s="2">
         <f t="shared" si="3"/>
         <v>26973.464853191454</v>
       </c>
-      <c r="G25" s="2">
+      <c r="H25" s="2">
         <f t="shared" si="2"/>
         <v>269.73464853191456</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>24</v>
       </c>
-      <c r="B26">
+      <c r="B26" s="2">
         <f t="shared" si="0"/>
         <v>1269.7346485319142</v>
       </c>
-      <c r="E26" s="2">
+      <c r="F26" s="3">
         <v>24</v>
       </c>
-      <c r="F26" s="2">
+      <c r="G26" s="2">
         <f t="shared" si="3"/>
         <v>28243.199501723368</v>
       </c>
-      <c r="G26" s="2">
+      <c r="H26" s="2">
         <f t="shared" si="2"/>
         <v>282.4319950172337</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>25</v>
       </c>
-      <c r="B27">
+      <c r="B27" s="2">
         <f t="shared" si="0"/>
         <v>1282.4319950172332</v>
       </c>
-      <c r="E27" s="2">
+      <c r="F27" s="3">
         <v>25</v>
       </c>
-      <c r="F27" s="2">
+      <c r="G27" s="2">
         <f t="shared" si="3"/>
         <v>29525.6314967406</v>
       </c>
-      <c r="G27" s="2">
+      <c r="H27" s="2">
         <f t="shared" si="2"/>
         <v>295.25631496740601</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>26</v>
       </c>
-      <c r="B28">
+      <c r="B28" s="2">
         <f t="shared" si="0"/>
         <v>1295.2563149674056</v>
       </c>
-      <c r="E28" s="2">
+      <c r="F28" s="3">
         <v>26</v>
       </c>
-      <c r="F28" s="2">
+      <c r="G28" s="2">
         <f t="shared" si="3"/>
         <v>30820.887811708006</v>
       </c>
-      <c r="G28" s="2">
+      <c r="H28" s="2">
         <f t="shared" si="2"/>
         <v>308.20887811708008</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>27</v>
       </c>
-      <c r="B29">
+      <c r="B29" s="2">
         <f t="shared" si="0"/>
         <v>1308.2088781170796</v>
       </c>
-      <c r="E29" s="2">
+      <c r="F29" s="3">
         <v>27</v>
       </c>
-      <c r="F29" s="2">
+      <c r="G29" s="2">
         <f t="shared" si="3"/>
         <v>32129.096689825084</v>
       </c>
-      <c r="G29" s="2">
+      <c r="H29" s="2">
         <f t="shared" si="2"/>
         <v>321.29096689825087</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>28</v>
       </c>
-      <c r="B30">
+      <c r="B30" s="2">
         <f t="shared" si="0"/>
         <v>1321.2909668982504</v>
       </c>
-      <c r="E30" s="2">
+      <c r="F30" s="3">
         <v>28</v>
       </c>
-      <c r="F30" s="2">
+      <c r="G30" s="2">
         <f t="shared" si="3"/>
         <v>33450.387656723338</v>
       </c>
-      <c r="G30" s="2">
+      <c r="H30" s="2">
         <f t="shared" si="2"/>
         <v>334.50387656723336</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>29</v>
       </c>
-      <c r="B31">
+      <c r="B31" s="2">
         <f t="shared" si="0"/>
         <v>1334.503876567233</v>
       </c>
-      <c r="E31" s="2">
+      <c r="F31" s="3">
         <v>29</v>
       </c>
-      <c r="F31" s="2">
+      <c r="G31" s="2">
         <f t="shared" si="3"/>
         <v>34784.891533290574</v>
       </c>
-      <c r="G31" s="2">
+      <c r="H31" s="2">
         <f t="shared" si="2"/>
         <v>347.84891533290573</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>30</v>
       </c>
-      <c r="B32">
+      <c r="B32" s="2">
         <f t="shared" si="0"/>
         <v>1347.8489153329053</v>
       </c>
-      <c r="E32" s="2">
+      <c r="F32" s="3">
         <v>30</v>
       </c>
-      <c r="F32" s="2">
+      <c r="G32" s="2">
         <f t="shared" si="3"/>
         <v>36132.740448623481</v>
       </c>
-      <c r="G32" s="2">
+      <c r="H32" s="2">
         <f t="shared" si="2"/>
         <v>361.3274044862348</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>31</v>
       </c>
-      <c r="B33">
+      <c r="B33" s="2">
         <f t="shared" si="0"/>
         <v>1361.3274044862344</v>
       </c>
-      <c r="E33" s="2">
+      <c r="F33" s="3">
         <v>31</v>
       </c>
-      <c r="F33" s="2">
+      <c r="G33" s="2">
         <f t="shared" si="3"/>
         <v>37494.067853109715</v>
       </c>
-      <c r="G33" s="2">
+      <c r="H33" s="2">
         <f t="shared" si="2"/>
         <v>374.94067853109715</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>32</v>
       </c>
-      <c r="B34">
+      <c r="B34" s="2">
         <f t="shared" si="0"/>
         <v>1374.9406785310966</v>
       </c>
-      <c r="E34" s="2">
+      <c r="F34" s="3">
         <v>32</v>
       </c>
-      <c r="F34" s="2">
+      <c r="G34" s="2">
         <f t="shared" si="3"/>
         <v>38869.008531640815</v>
       </c>
-      <c r="G34" s="2">
+      <c r="H34" s="2">
         <f t="shared" si="2"/>
         <v>388.69008531640816</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>33</v>
       </c>
-      <c r="B35">
+      <c r="B35" s="2">
         <f t="shared" si="0"/>
         <v>1388.6900853164077</v>
       </c>
-      <c r="E35" s="2">
+      <c r="F35" s="3">
         <v>33</v>
       </c>
-      <c r="F35" s="2">
+      <c r="G35" s="2">
         <f t="shared" si="3"/>
         <v>40257.698616957226</v>
       </c>
-      <c r="G35" s="2">
+      <c r="H35" s="2">
         <f t="shared" si="2"/>
         <v>402.57698616957225</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>34</v>
       </c>
-      <c r="B36">
+      <c r="B36" s="2">
         <f t="shared" si="0"/>
         <v>1402.5769861695717</v>
       </c>
-      <c r="E36" s="2">
+      <c r="F36" s="3">
         <v>34</v>
       </c>
-      <c r="F36" s="2">
+      <c r="G36" s="2">
         <f t="shared" si="3"/>
         <v>41660.2756031268</v>
       </c>
-      <c r="G36" s="2">
+      <c r="H36" s="2">
         <f t="shared" si="2"/>
         <v>416.60275603126803</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>35</v>
       </c>
-      <c r="B37">
+      <c r="B37" s="2">
         <f t="shared" si="0"/>
         <v>1416.6027560312673</v>
       </c>
-      <c r="E37" s="2">
+      <c r="F37" s="3">
         <v>35</v>
       </c>
-      <c r="F37" s="2">
+      <c r="G37" s="2">
         <f t="shared" si="3"/>
         <v>43076.878359158065</v>
       </c>
-      <c r="G37" s="2">
+      <c r="H37" s="2">
         <f t="shared" si="2"/>
         <v>430.76878359158064</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>36</v>
       </c>
-      <c r="B38">
+      <c r="B38" s="2">
         <f t="shared" si="0"/>
         <v>1430.7687835915799</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="3">
         <v>36</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <f t="shared" si="3"/>
         <v>44507.647142749644</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <f t="shared" si="2"/>
         <v>445.07647142749647</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>37</v>
       </c>
-      <c r="B39">
+      <c r="B39" s="2">
         <f t="shared" si="0"/>
         <v>1445.0764714274958</v>
       </c>
-      <c r="E39" s="2">
+      <c r="F39" s="3">
         <v>37</v>
       </c>
-      <c r="F39" s="2">
+      <c r="G39" s="2">
         <f t="shared" si="3"/>
         <v>45952.723614177143</v>
       </c>
-      <c r="G39" s="2">
+      <c r="H39" s="2">
         <f t="shared" si="2"/>
         <v>459.52723614177143</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>38</v>
       </c>
-      <c r="B40">
+      <c r="B40" s="2">
         <f t="shared" si="0"/>
         <v>1459.5272361417708</v>
       </c>
-      <c r="E40" s="2">
+      <c r="F40" s="3">
         <v>38</v>
       </c>
-      <c r="F40" s="2">
+      <c r="G40" s="2">
         <f t="shared" si="3"/>
         <v>47412.250850318916</v>
       </c>
-      <c r="G40" s="2">
+      <c r="H40" s="2">
         <f t="shared" si="2"/>
         <v>474.12250850318918</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>39</v>
       </c>
-      <c r="B41">
+      <c r="B41" s="2">
         <f t="shared" si="0"/>
         <v>1474.1225085031886</v>
       </c>
-      <c r="E41" s="2">
+      <c r="F41" s="3">
         <v>39</v>
       </c>
-      <c r="F41" s="2">
+      <c r="G41" s="2">
         <f t="shared" si="3"/>
         <v>48886.373358822108</v>
       </c>
-      <c r="G41" s="2">
+      <c r="H41" s="2">
         <f t="shared" si="2"/>
         <v>488.86373358822107</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>40</v>
       </c>
-      <c r="B42">
+      <c r="B42" s="2">
         <f t="shared" si="0"/>
         <v>1488.8637335882204</v>
       </c>
-      <c r="E42" s="2">
+      <c r="F42" s="3">
         <v>40</v>
       </c>
-      <c r="F42" s="2">
+      <c r="G42" s="2">
         <f t="shared" si="3"/>
         <v>50375.237092410331</v>
       </c>
-      <c r="G42" s="2">
+      <c r="H42" s="2">
         <f t="shared" si="2"/>
         <v>503.75237092410333</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>41</v>
       </c>
-      <c r="B43">
+      <c r="B43" s="2">
         <f t="shared" si="0"/>
         <v>1503.7523709241025</v>
       </c>
-      <c r="E43" s="2">
+      <c r="F43" s="3">
         <v>41</v>
       </c>
-      <c r="F43" s="2">
+      <c r="G43" s="2">
         <f t="shared" si="3"/>
         <v>51878.989463334437</v>
       </c>
-      <c r="G43" s="2">
+      <c r="H43" s="2">
         <f t="shared" si="2"/>
         <v>518.78989463334437</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>42</v>
       </c>
-      <c r="B44">
+      <c r="B44" s="2">
         <f t="shared" si="0"/>
         <v>1518.7898946333435</v>
       </c>
-      <c r="E44" s="2">
+      <c r="F44" s="3">
         <v>42</v>
       </c>
-      <c r="F44" s="2">
+      <c r="G44" s="2">
         <f t="shared" si="3"/>
         <v>53397.779357967782</v>
       </c>
-      <c r="G44" s="2">
+      <c r="H44" s="2">
         <f t="shared" si="2"/>
         <v>533.97779357967784</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>43</v>
       </c>
-      <c r="B45">
+      <c r="B45" s="2">
         <f t="shared" si="0"/>
         <v>1533.9777935796769</v>
       </c>
-      <c r="E45" s="2">
+      <c r="F45" s="3">
         <v>43</v>
       </c>
-      <c r="F45" s="2">
+      <c r="G45" s="2">
         <f t="shared" si="3"/>
         <v>54931.757151547463</v>
       </c>
-      <c r="G45" s="2">
+      <c r="H45" s="2">
         <f t="shared" si="2"/>
         <v>549.3175715154747</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>44</v>
       </c>
-      <c r="B46">
+      <c r="B46" s="2">
         <f t="shared" si="0"/>
         <v>1549.3175715154737</v>
       </c>
-      <c r="E46" s="2">
+      <c r="F46" s="3">
         <v>44</v>
       </c>
-      <c r="F46" s="2">
+      <c r="G46" s="2">
         <f t="shared" si="3"/>
         <v>56481.074723062935</v>
       </c>
-      <c r="G46" s="2">
+      <c r="H46" s="2">
         <f t="shared" si="2"/>
         <v>564.81074723062932</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>45</v>
       </c>
-      <c r="B47">
+      <c r="B47" s="2">
         <f t="shared" si="0"/>
         <v>1564.8107472306285</v>
       </c>
-      <c r="E47" s="2">
+      <c r="F47" s="3">
         <v>45</v>
       </c>
-      <c r="F47" s="2">
+      <c r="G47" s="2">
         <f t="shared" si="3"/>
         <v>58045.885470293564</v>
       </c>
-      <c r="G47" s="2">
+      <c r="H47" s="2">
         <f t="shared" si="2"/>
         <v>580.4588547029357</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>46</v>
       </c>
-      <c r="B48">
+      <c r="B48" s="2">
         <f t="shared" si="0"/>
         <v>1580.4588547029348</v>
       </c>
-      <c r="E48" s="2">
+      <c r="F48" s="3">
         <v>46</v>
       </c>
-      <c r="F48" s="2">
+      <c r="G48" s="2">
         <f t="shared" si="3"/>
         <v>59626.344324996498</v>
       </c>
-      <c r="G48" s="2">
+      <c r="H48" s="2">
         <f t="shared" si="2"/>
         <v>596.26344324996501</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>47</v>
       </c>
-      <c r="B49">
+      <c r="B49" s="2">
         <f t="shared" si="0"/>
         <v>1596.2634432499642</v>
       </c>
-      <c r="E49" s="2">
+      <c r="F49" s="3">
         <v>47</v>
       </c>
-      <c r="F49" s="2">
+      <c r="G49" s="2">
         <f t="shared" si="3"/>
         <v>61222.60776824646</v>
       </c>
-      <c r="G49" s="2">
+      <c r="H49" s="2">
         <f t="shared" si="2"/>
         <v>612.22607768246462</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>48</v>
       </c>
-      <c r="B50">
+      <c r="B50" s="2">
         <f t="shared" si="0"/>
         <v>1612.2260776824639</v>
       </c>
-      <c r="E50" s="2">
+      <c r="F50" s="3">
         <v>48</v>
       </c>
-      <c r="F50" s="2">
+      <c r="G50" s="2">
         <f t="shared" si="3"/>
         <v>62834.833845928923</v>
       </c>
-      <c r="G50" s="2">
+      <c r="H50" s="2">
         <f t="shared" si="2"/>
         <v>628.34833845928927</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>49</v>
       </c>
-      <c r="B51">
+      <c r="B51" s="2">
         <f t="shared" si="0"/>
         <v>1628.3483384592885</v>
       </c>
-      <c r="E51" s="2">
+      <c r="F51" s="3">
         <v>49</v>
       </c>
-      <c r="F51" s="2">
+      <c r="G51" s="2">
         <f t="shared" si="3"/>
         <v>64463.182184388213</v>
       </c>
-      <c r="G51" s="2">
+      <c r="H51" s="2">
         <f t="shared" si="2"/>
         <v>644.63182184388211</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>50</v>
       </c>
-      <c r="B52">
+      <c r="B52" s="2">
         <f t="shared" si="0"/>
         <v>1644.6318218438814</v>
       </c>
-      <c r="E52" s="2">
+      <c r="F52" s="3">
         <v>50</v>
       </c>
-      <c r="F52" s="2">
+      <c r="G52" s="2">
         <f t="shared" si="3"/>
         <v>66107.814006232104</v>
       </c>
-      <c r="G52" s="2">
+      <c r="H52" s="2">
         <f t="shared" si="2"/>
         <v>661.07814006232104</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>51</v>
       </c>
-      <c r="B53">
+      <c r="B53" s="2">
         <f t="shared" si="0"/>
         <v>1661.0781400623202</v>
       </c>
-      <c r="E53" s="2">
+      <c r="F53" s="3">
         <v>51</v>
       </c>
-      <c r="F53" s="2">
+      <c r="G53" s="2">
         <f t="shared" si="3"/>
         <v>67768.892146294427</v>
       </c>
-      <c r="G53" s="2">
+      <c r="H53" s="2">
         <f t="shared" si="2"/>
         <v>677.68892146294434</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>52</v>
       </c>
-      <c r="B54">
+      <c r="B54" s="2">
         <f t="shared" si="0"/>
         <v>1677.6889214629434</v>
       </c>
-      <c r="E54" s="2">
+      <c r="F54" s="3">
         <v>52</v>
       </c>
-      <c r="F54" s="2">
+      <c r="G54" s="2">
         <f t="shared" si="3"/>
         <v>69446.581067757375</v>
       </c>
-      <c r="G54" s="2">
+      <c r="H54" s="2">
         <f t="shared" si="2"/>
         <v>694.46581067757381</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>53</v>
       </c>
-      <c r="B55">
+      <c r="B55" s="2">
         <f t="shared" si="0"/>
         <v>1694.4658106775728</v>
       </c>
-      <c r="E55" s="2">
+      <c r="F55" s="3">
         <v>53</v>
       </c>
-      <c r="F55" s="2">
+      <c r="G55" s="2">
         <f t="shared" si="3"/>
         <v>71141.04687843495</v>
       </c>
-      <c r="G55" s="2">
+      <c r="H55" s="2">
         <f t="shared" si="2"/>
         <v>711.41046878434952</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>54</v>
       </c>
-      <c r="B56">
+      <c r="B56" s="2">
         <f t="shared" si="0"/>
         <v>1711.4104687843485</v>
       </c>
-      <c r="E56" s="2">
+      <c r="F56" s="3">
         <v>54</v>
       </c>
-      <c r="F56" s="2">
+      <c r="G56" s="2">
         <f t="shared" si="3"/>
         <v>72852.457347219301</v>
       </c>
-      <c r="G56" s="2">
+      <c r="H56" s="2">
         <f t="shared" si="2"/>
         <v>728.52457347219297</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>55</v>
       </c>
-      <c r="B57">
+      <c r="B57" s="2">
         <f t="shared" si="0"/>
         <v>1728.5245734721921</v>
       </c>
-      <c r="E57" s="2">
+      <c r="F57" s="3">
         <v>55</v>
       </c>
-      <c r="F57" s="2">
+      <c r="G57" s="2">
         <f t="shared" si="3"/>
         <v>74580.981920691498</v>
       </c>
-      <c r="G57" s="2">
+      <c r="H57" s="2">
         <f t="shared" si="2"/>
         <v>745.80981920691499</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>56</v>
       </c>
-      <c r="B58">
+      <c r="B58" s="2">
         <f t="shared" si="0"/>
         <v>1745.809819206914</v>
       </c>
-      <c r="E58" s="2">
+      <c r="F58" s="3">
         <v>56</v>
       </c>
-      <c r="F58" s="2">
+      <c r="G58" s="2">
         <f t="shared" si="3"/>
         <v>76326.791739898414</v>
       </c>
-      <c r="G58" s="2">
+      <c r="H58" s="2">
         <f t="shared" si="2"/>
         <v>763.2679173989842</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>57</v>
       </c>
-      <c r="B59">
+      <c r="B59" s="2">
         <f t="shared" si="0"/>
         <v>1763.2679173989832</v>
       </c>
-      <c r="E59" s="2">
+      <c r="F59" s="3">
         <v>57</v>
       </c>
-      <c r="F59" s="2">
+      <c r="G59" s="2">
         <f t="shared" si="3"/>
         <v>78090.059657297403</v>
       </c>
-      <c r="G59" s="2">
+      <c r="H59" s="2">
         <f t="shared" si="2"/>
         <v>780.900596572974</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>58</v>
       </c>
-      <c r="B60">
+      <c r="B60" s="2">
         <f t="shared" si="0"/>
         <v>1780.900596572973</v>
       </c>
-      <c r="E60" s="2">
+      <c r="F60" s="3">
         <v>58</v>
       </c>
-      <c r="F60" s="2">
+      <c r="G60" s="2">
         <f t="shared" si="3"/>
         <v>79870.960253870377</v>
       </c>
-      <c r="G60" s="2">
+      <c r="H60" s="2">
         <f t="shared" si="2"/>
         <v>798.70960253870373</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>59</v>
       </c>
-      <c r="B61">
+      <c r="B61" s="2">
         <f t="shared" si="0"/>
         <v>1798.7096025387027</v>
       </c>
-      <c r="E61" s="2">
+      <c r="F61" s="3">
         <v>59</v>
       </c>
-      <c r="F61" s="2">
+      <c r="G61" s="2">
         <f t="shared" si="3"/>
         <v>81669.669856409077</v>
       </c>
-      <c r="G61" s="2">
+      <c r="H61" s="2">
         <f t="shared" si="2"/>
         <v>816.69669856409075</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>60</v>
       </c>
-      <c r="B62">
+      <c r="B62" s="2">
         <f t="shared" si="0"/>
         <v>1816.6966985640897</v>
       </c>
-      <c r="E62" s="2">
+      <c r="F62" s="3">
         <v>60</v>
       </c>
-      <c r="F62" s="2">
+      <c r="G62" s="2">
         <f t="shared" si="3"/>
         <v>83486.366554973167</v>
       </c>
-      <c r="G62" s="2">
+      <c r="H62" s="2">
         <f t="shared" si="2"/>
         <v>834.86366554973165</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>61</v>
       </c>
-      <c r="B63">
+      <c r="B63" s="2">
         <f t="shared" si="0"/>
         <v>1834.8636655497307</v>
       </c>
-      <c r="E63" s="2">
+      <c r="F63" s="3">
         <v>61</v>
       </c>
-      <c r="F63" s="2">
+      <c r="G63" s="2">
         <f t="shared" si="3"/>
         <v>85321.230220522892</v>
       </c>
-      <c r="G63" s="2">
+      <c r="H63" s="2">
         <f t="shared" si="2"/>
         <v>853.21230220522898</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>62</v>
       </c>
-      <c r="B64">
+      <c r="B64" s="2">
         <f t="shared" si="0"/>
         <v>1853.2123022052281</v>
       </c>
-      <c r="E64" s="2">
+      <c r="F64" s="3">
         <v>62</v>
       </c>
-      <c r="F64" s="2">
+      <c r="G64" s="2">
         <f t="shared" si="3"/>
         <v>87174.442522728117</v>
       </c>
-      <c r="G64" s="2">
+      <c r="H64" s="2">
         <f t="shared" si="2"/>
         <v>871.74442522728123</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>63</v>
       </c>
-      <c r="B65">
+      <c r="B65" s="2">
         <f t="shared" si="0"/>
         <v>1871.7444252272803</v>
       </c>
-      <c r="E65" s="2">
+      <c r="F65" s="3">
         <v>63</v>
       </c>
-      <c r="F65" s="2">
+      <c r="G65" s="2">
         <f t="shared" si="3"/>
         <v>89046.186947955401</v>
       </c>
-      <c r="G65" s="2">
+      <c r="H65" s="2">
         <f t="shared" si="2"/>
         <v>890.46186947955403</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>64</v>
       </c>
-      <c r="B66">
+      <c r="B66" s="2">
         <f t="shared" si="0"/>
         <v>1890.4618694795531</v>
       </c>
-      <c r="E66" s="2">
+      <c r="F66" s="3">
         <v>64</v>
       </c>
-      <c r="F66" s="2">
+      <c r="G66" s="2">
         <f t="shared" si="3"/>
         <v>90936.648817434951</v>
       </c>
-      <c r="G66" s="2">
+      <c r="H66" s="2">
         <f t="shared" si="2"/>
         <v>909.36648817434957</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>65</v>
       </c>
-      <c r="B67">
+      <c r="B67" s="2">
         <f t="shared" si="0"/>
         <v>1909.3664881743487</v>
       </c>
-      <c r="E67" s="2">
+      <c r="F67" s="3">
         <v>65</v>
       </c>
-      <c r="F67" s="2">
+      <c r="G67" s="2">
         <f t="shared" si="3"/>
         <v>92846.015305609297</v>
       </c>
-      <c r="G67" s="2">
+      <c r="H67" s="2">
         <f t="shared" si="2"/>
         <v>928.46015305609296</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>66</v>
       </c>
-      <c r="B68">
-        <f t="shared" ref="B68:B122" si="4">B67+B67*$D$3</f>
+      <c r="B68" s="2">
+        <f t="shared" ref="B68:B122" si="4">B67+B67*$E$3</f>
         <v>1928.4601530560922</v>
       </c>
-      <c r="E68" s="2">
+      <c r="F68" s="3">
         <v>66</v>
       </c>
-      <c r="F68" s="2">
+      <c r="G68" s="2">
         <f t="shared" si="3"/>
         <v>94774.475458665387</v>
       </c>
-      <c r="G68" s="2">
-        <f t="shared" ref="G68:G122" si="5">F68*$D$3</f>
+      <c r="H68" s="2">
+        <f t="shared" ref="H68:H122" si="5">G68*$E$3</f>
         <v>947.74475458665393</v>
       </c>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>67</v>
       </c>
-      <c r="B69">
+      <c r="B69" s="2">
         <f t="shared" si="4"/>
         <v>1947.744754586653</v>
       </c>
-      <c r="E69" s="2">
+      <c r="F69" s="3">
         <v>67</v>
       </c>
-      <c r="F69" s="2">
+      <c r="G69" s="2">
         <f t="shared" si="3"/>
         <v>96722.220213252047</v>
       </c>
-      <c r="G69" s="2">
+      <c r="H69" s="2">
         <f t="shared" si="5"/>
         <v>967.22220213252047</v>
       </c>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>68</v>
       </c>
-      <c r="B70">
+      <c r="B70" s="2">
         <f t="shared" si="4"/>
         <v>1967.2222021325194</v>
       </c>
-      <c r="E70" s="2">
+      <c r="F70" s="3">
         <v>68</v>
       </c>
-      <c r="F70" s="2">
+      <c r="G70" s="2">
         <f t="shared" si="3"/>
         <v>98689.442415384561</v>
       </c>
-      <c r="G70" s="2">
+      <c r="H70" s="2">
         <f t="shared" si="5"/>
         <v>986.89442415384565</v>
       </c>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>69</v>
       </c>
-      <c r="B71">
+      <c r="B71" s="2">
         <f t="shared" si="4"/>
         <v>1986.8944241538447</v>
       </c>
-      <c r="E71" s="2">
+      <c r="F71" s="3">
         <v>69</v>
       </c>
-      <c r="F71" s="2">
+      <c r="G71" s="2">
         <f t="shared" si="3"/>
         <v>100676.3368395384</v>
       </c>
-      <c r="G71" s="2">
+      <c r="H71" s="2">
         <f t="shared" si="5"/>
         <v>1006.7633683953841</v>
       </c>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>70</v>
       </c>
-      <c r="B72">
+      <c r="B72" s="2">
         <f t="shared" si="4"/>
         <v>2006.7633683953832</v>
       </c>
-      <c r="E72" s="2">
+      <c r="F72" s="3">
         <v>70</v>
       </c>
-      <c r="F72" s="2">
+      <c r="G72" s="2">
         <f t="shared" si="3"/>
         <v>102683.10020793379</v>
       </c>
-      <c r="G72" s="2">
+      <c r="H72" s="2">
         <f t="shared" si="5"/>
         <v>1026.8310020793378</v>
       </c>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>71</v>
       </c>
-      <c r="B73">
+      <c r="B73" s="2">
         <f t="shared" si="4"/>
         <v>2026.8310020793369</v>
       </c>
-      <c r="E73" s="2">
+      <c r="F73" s="3">
         <v>71</v>
       </c>
-      <c r="F73" s="2">
+      <c r="G73" s="2">
         <f t="shared" si="3"/>
         <v>104709.93121001314</v>
       </c>
-      <c r="G73" s="2">
+      <c r="H73" s="2">
         <f t="shared" si="5"/>
         <v>1047.0993121001313</v>
       </c>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>72</v>
       </c>
-      <c r="B74">
+      <c r="B74" s="2">
         <f t="shared" si="4"/>
         <v>2047.0993121001304</v>
       </c>
-      <c r="E74" s="2">
+      <c r="F74" s="3">
         <v>72</v>
       </c>
-      <c r="F74" s="2">
+      <c r="G74" s="2">
         <f t="shared" si="3"/>
         <v>106757.03052211327</v>
       </c>
-      <c r="G74" s="2">
+      <c r="H74" s="2">
         <f t="shared" si="5"/>
         <v>1067.5703052211327</v>
       </c>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>73</v>
       </c>
-      <c r="B75">
+      <c r="B75" s="2">
         <f t="shared" si="4"/>
         <v>2067.5703052211315</v>
       </c>
-      <c r="E75" s="2">
+      <c r="F75" s="3">
         <v>73</v>
       </c>
-      <c r="F75" s="2">
+      <c r="G75" s="2">
         <f t="shared" si="3"/>
         <v>108824.60082733441</v>
       </c>
-      <c r="G75" s="2">
+      <c r="H75" s="2">
         <f t="shared" si="5"/>
         <v>1088.2460082733442</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>74</v>
       </c>
-      <c r="B76">
+      <c r="B76" s="2">
         <f t="shared" si="4"/>
         <v>2088.2460082733428</v>
       </c>
-      <c r="E76" s="2">
+      <c r="F76" s="3">
         <v>74</v>
       </c>
-      <c r="F76" s="2">
-        <f t="shared" ref="F76:F95" si="6">F75+G75+$D$2</f>
+      <c r="G76" s="2">
+        <f t="shared" ref="G76:G95" si="6">G75+H75+$E$2</f>
         <v>110912.84683560775</v>
       </c>
-      <c r="G76" s="2">
+      <c r="H76" s="2">
         <f t="shared" si="5"/>
         <v>1109.1284683560775</v>
       </c>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>75</v>
       </c>
-      <c r="B77">
+      <c r="B77" s="2">
         <f t="shared" si="4"/>
         <v>2109.1284683560762</v>
       </c>
-      <c r="E77" s="2">
+      <c r="F77" s="3">
         <v>75</v>
       </c>
-      <c r="F77" s="2">
+      <c r="G77" s="2">
         <f t="shared" si="6"/>
         <v>113021.97530396383</v>
       </c>
-      <c r="G77" s="2">
+      <c r="H77" s="2">
         <f t="shared" si="5"/>
         <v>1130.2197530396384</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>76</v>
       </c>
-      <c r="B78">
+      <c r="B78" s="2">
         <f t="shared" si="4"/>
         <v>2130.219753039637</v>
       </c>
-      <c r="E78" s="2">
+      <c r="F78" s="3">
         <v>76</v>
       </c>
-      <c r="F78" s="2">
+      <c r="G78" s="2">
         <f t="shared" si="6"/>
         <v>115152.19505700347</v>
       </c>
-      <c r="G78" s="2">
+      <c r="H78" s="2">
         <f t="shared" si="5"/>
         <v>1151.5219505700347</v>
       </c>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>77</v>
       </c>
-      <c r="B79">
+      <c r="B79" s="2">
         <f t="shared" si="4"/>
         <v>2151.5219505700334</v>
       </c>
-      <c r="E79" s="2">
+      <c r="F79" s="3">
         <v>77</v>
       </c>
-      <c r="F79" s="2">
+      <c r="G79" s="2">
         <f t="shared" si="6"/>
         <v>117303.7170075735</v>
       </c>
-      <c r="G79" s="2">
+      <c r="H79" s="2">
         <f t="shared" si="5"/>
         <v>1173.037170075735</v>
       </c>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>78</v>
       </c>
-      <c r="B80">
+      <c r="B80" s="2">
         <f t="shared" si="4"/>
         <v>2173.0371700757337</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="3">
         <v>78</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <f t="shared" si="6"/>
         <v>119476.75417764924</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <f t="shared" si="5"/>
         <v>1194.7675417764924</v>
       </c>
     </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>79</v>
       </c>
-      <c r="B81">
+      <c r="B81" s="2">
         <f t="shared" si="4"/>
         <v>2194.7675417764908</v>
       </c>
-      <c r="E81" s="2">
+      <c r="F81" s="3">
         <v>79</v>
       </c>
-      <c r="F81" s="2">
+      <c r="G81" s="2">
         <f t="shared" si="6"/>
         <v>121671.52171942574</v>
       </c>
-      <c r="G81" s="2">
+      <c r="H81" s="2">
         <f t="shared" si="5"/>
         <v>1216.7152171942575</v>
       </c>
     </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>80</v>
       </c>
-      <c r="B82">
+      <c r="B82" s="2">
         <f t="shared" si="4"/>
         <v>2216.7152171942557</v>
       </c>
-      <c r="E82" s="2">
+      <c r="F82" s="3">
         <v>80</v>
       </c>
-      <c r="F82" s="2">
+      <c r="G82" s="2">
         <f t="shared" si="6"/>
         <v>123888.23693662</v>
       </c>
-      <c r="G82" s="2">
+      <c r="H82" s="2">
         <f t="shared" si="5"/>
         <v>1238.8823693662</v>
       </c>
     </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>81</v>
       </c>
-      <c r="B83">
+      <c r="B83" s="2">
         <f t="shared" si="4"/>
         <v>2238.8823693661984</v>
       </c>
-      <c r="E83" s="2">
+      <c r="F83" s="3">
         <v>81</v>
       </c>
-      <c r="F83" s="2">
+      <c r="G83" s="2">
         <f t="shared" si="6"/>
         <v>126127.1193059862</v>
       </c>
-      <c r="G83" s="2">
+      <c r="H83" s="2">
         <f t="shared" si="5"/>
         <v>1261.2711930598621</v>
       </c>
     </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>82</v>
       </c>
-      <c r="B84">
+      <c r="B84" s="2">
         <f t="shared" si="4"/>
         <v>2261.2711930598603</v>
       </c>
-      <c r="E84" s="2">
+      <c r="F84" s="3">
         <v>82</v>
       </c>
-      <c r="F84" s="2">
+      <c r="G84" s="2">
         <f t="shared" si="6"/>
         <v>128388.39049904606</v>
       </c>
-      <c r="G84" s="2">
+      <c r="H84" s="2">
         <f t="shared" si="5"/>
         <v>1283.8839049904607</v>
       </c>
     </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>83</v>
       </c>
-      <c r="B85">
+      <c r="B85" s="2">
         <f t="shared" si="4"/>
         <v>2283.8839049904586</v>
       </c>
-      <c r="E85" s="2">
+      <c r="F85" s="3">
         <v>83</v>
       </c>
-      <c r="F85" s="2">
+      <c r="G85" s="2">
         <f t="shared" si="6"/>
         <v>130672.27440403652</v>
       </c>
-      <c r="G85" s="2">
+      <c r="H85" s="2">
         <f t="shared" si="5"/>
         <v>1306.7227440403653</v>
       </c>
     </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>84</v>
       </c>
-      <c r="B86">
+      <c r="B86" s="2">
         <f t="shared" si="4"/>
         <v>2306.7227440403631</v>
       </c>
-      <c r="E86" s="2">
+      <c r="F86" s="3">
         <v>84</v>
       </c>
-      <c r="F86" s="2">
+      <c r="G86" s="2">
         <f t="shared" si="6"/>
         <v>132978.99714807689</v>
       </c>
-      <c r="G86" s="2">
+      <c r="H86" s="2">
         <f t="shared" si="5"/>
         <v>1329.7899714807688</v>
       </c>
     </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>85</v>
       </c>
-      <c r="B87">
+      <c r="B87" s="2">
         <f t="shared" si="4"/>
         <v>2329.7899714807668</v>
       </c>
-      <c r="E87" s="2">
+      <c r="F87" s="3">
         <v>85</v>
       </c>
-      <c r="F87" s="2">
+      <c r="G87" s="2">
         <f t="shared" si="6"/>
         <v>135308.78711955764</v>
       </c>
-      <c r="G87" s="2">
+      <c r="H87" s="2">
         <f t="shared" si="5"/>
         <v>1353.0878711955766</v>
       </c>
     </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>86</v>
       </c>
-      <c r="B88">
+      <c r="B88" s="2">
         <f t="shared" si="4"/>
         <v>2353.0878711955743</v>
       </c>
-      <c r="E88" s="2">
+      <c r="F88" s="3">
         <v>86</v>
       </c>
-      <c r="F88" s="2">
+      <c r="G88" s="2">
         <f t="shared" si="6"/>
         <v>137661.87499075322</v>
       </c>
-      <c r="G88" s="2">
+      <c r="H88" s="2">
         <f t="shared" si="5"/>
         <v>1376.6187499075322</v>
       </c>
     </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>87</v>
       </c>
-      <c r="B89">
+      <c r="B89" s="2">
         <f t="shared" si="4"/>
         <v>2376.6187499075299</v>
       </c>
-      <c r="E89" s="2">
+      <c r="F89" s="3">
         <v>87</v>
       </c>
-      <c r="F89" s="2">
+      <c r="G89" s="2">
         <f t="shared" si="6"/>
         <v>140038.49374066075</v>
       </c>
-      <c r="G89" s="2">
+      <c r="H89" s="2">
         <f t="shared" si="5"/>
         <v>1400.3849374066076</v>
       </c>
     </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>88</v>
       </c>
-      <c r="B90">
+      <c r="B90" s="2">
         <f t="shared" si="4"/>
         <v>2400.3849374066053</v>
       </c>
-      <c r="E90" s="2">
+      <c r="F90" s="3">
         <v>88</v>
       </c>
-      <c r="F90" s="2">
+      <c r="G90" s="2">
         <f t="shared" si="6"/>
         <v>142438.87867806735</v>
       </c>
-      <c r="G90" s="2">
+      <c r="H90" s="2">
         <f t="shared" si="5"/>
         <v>1424.3887867806736</v>
       </c>
     </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>89</v>
       </c>
-      <c r="B91">
+      <c r="B91" s="2">
         <f t="shared" si="4"/>
         <v>2424.3887867806716</v>
       </c>
-      <c r="E91" s="2">
+      <c r="F91" s="3">
         <v>89</v>
       </c>
-      <c r="F91" s="2">
+      <c r="G91" s="2">
         <f t="shared" si="6"/>
         <v>144863.26746484803</v>
       </c>
-      <c r="G91" s="2">
+      <c r="H91" s="2">
         <f t="shared" si="5"/>
         <v>1448.6326746484804</v>
       </c>
     </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>90</v>
       </c>
-      <c r="B92">
+      <c r="B92" s="2">
         <f t="shared" si="4"/>
         <v>2448.6326746484783</v>
       </c>
-      <c r="E92" s="2">
+      <c r="F92" s="3">
         <v>90</v>
       </c>
-      <c r="F92" s="2">
+      <c r="G92" s="2">
         <f t="shared" si="6"/>
         <v>147311.90013949652</v>
       </c>
-      <c r="G92" s="2">
+      <c r="H92" s="2">
         <f t="shared" si="5"/>
         <v>1473.1190013949652</v>
       </c>
     </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>91</v>
       </c>
-      <c r="B93">
+      <c r="B93" s="2">
         <f t="shared" si="4"/>
         <v>2473.1190013949631</v>
       </c>
-      <c r="E93" s="2">
+      <c r="F93" s="3">
         <v>91</v>
       </c>
-      <c r="F93" s="2">
+      <c r="G93" s="2">
         <f t="shared" si="6"/>
         <v>149785.01914089147</v>
       </c>
-      <c r="G93" s="2">
+      <c r="H93" s="2">
         <f t="shared" si="5"/>
         <v>1497.8501914089147</v>
       </c>
     </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>92</v>
       </c>
-      <c r="B94">
+      <c r="B94" s="2">
         <f t="shared" si="4"/>
         <v>2497.8501914089129</v>
       </c>
-      <c r="E94" s="2">
+      <c r="F94" s="3">
         <v>92</v>
       </c>
-      <c r="F94" s="2">
+      <c r="G94" s="2">
         <f t="shared" si="6"/>
         <v>152282.86933230038</v>
       </c>
-      <c r="G94" s="2">
+      <c r="H94" s="2">
         <f t="shared" si="5"/>
         <v>1522.8286933230038</v>
       </c>
     </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>93</v>
       </c>
-      <c r="B95">
+      <c r="B95" s="2">
         <f t="shared" si="4"/>
         <v>2522.828693323002</v>
       </c>
-      <c r="E95" s="2">
+      <c r="F95" s="3">
         <v>93</v>
       </c>
-      <c r="F95" s="2">
+      <c r="G95" s="2">
         <f t="shared" si="6"/>
         <v>154805.69802562339</v>
       </c>
-      <c r="G95" s="2">
+      <c r="H95" s="2">
         <f t="shared" si="5"/>
         <v>1548.0569802562341</v>
       </c>
     </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>94</v>
       </c>
-      <c r="B96">
+      <c r="B96" s="2">
         <f t="shared" si="4"/>
         <v>2548.0569802562318</v>
       </c>
-      <c r="E96" s="2">
+      <c r="F96" s="3">
         <v>94</v>
       </c>
-      <c r="F96" s="2">
-        <f t="shared" ref="F96:F101" si="7">F95+G95+$D$2</f>
+      <c r="G96" s="2">
+        <f t="shared" ref="G96:G101" si="7">G95+H95+$E$2</f>
         <v>157353.75500587962</v>
       </c>
-      <c r="G96" s="2">
+      <c r="H96" s="2">
         <f t="shared" si="5"/>
         <v>1573.5375500587961</v>
       </c>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>95</v>
       </c>
-      <c r="B97">
+      <c r="B97" s="2">
         <f t="shared" si="4"/>
         <v>2573.5375500587943</v>
       </c>
-      <c r="E97" s="2">
+      <c r="F97" s="3">
         <v>95</v>
       </c>
-      <c r="F97" s="2">
+      <c r="G97" s="2">
         <f t="shared" si="7"/>
         <v>159927.29255593842</v>
       </c>
-      <c r="G97" s="2">
+      <c r="H97" s="2">
         <f t="shared" si="5"/>
         <v>1599.2729255593842</v>
       </c>
     </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>96</v>
       </c>
-      <c r="B98">
+      <c r="B98" s="2">
         <f t="shared" si="4"/>
         <v>2599.2729255593822</v>
       </c>
-      <c r="E98" s="2">
+      <c r="F98" s="3">
         <v>96</v>
       </c>
-      <c r="F98" s="2">
+      <c r="G98" s="2">
         <f t="shared" si="7"/>
         <v>162526.56548149779</v>
       </c>
-      <c r="G98" s="2">
+      <c r="H98" s="2">
         <f t="shared" si="5"/>
         <v>1625.265654814978</v>
       </c>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>97</v>
       </c>
-      <c r="B99">
+      <c r="B99" s="2">
         <f t="shared" si="4"/>
         <v>2625.2656548149762</v>
       </c>
-      <c r="E99" s="2">
+      <c r="F99" s="3">
         <v>97</v>
       </c>
-      <c r="F99" s="2">
+      <c r="G99" s="2">
         <f t="shared" si="7"/>
         <v>165151.83113631277</v>
       </c>
-      <c r="G99" s="2">
+      <c r="H99" s="2">
         <f t="shared" si="5"/>
         <v>1651.5183113631279</v>
       </c>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>98</v>
       </c>
-      <c r="B100">
+      <c r="B100" s="2">
         <f t="shared" si="4"/>
         <v>2651.518311363126</v>
       </c>
-      <c r="E100" s="2">
+      <c r="F100" s="3">
         <v>98</v>
       </c>
-      <c r="F100" s="2">
+      <c r="G100" s="2">
         <f t="shared" si="7"/>
         <v>167803.34944767589</v>
       </c>
-      <c r="G100" s="2">
+      <c r="H100" s="2">
         <f t="shared" si="5"/>
         <v>1678.033494476759</v>
       </c>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>99</v>
       </c>
-      <c r="B101">
+      <c r="B101" s="2">
         <f t="shared" si="4"/>
         <v>2678.0334944767574</v>
       </c>
-      <c r="E101" s="2">
+      <c r="F101" s="3">
         <v>99</v>
       </c>
-      <c r="F101" s="2">
+      <c r="G101" s="2">
         <f t="shared" si="7"/>
         <v>170481.38294215265</v>
       </c>
-      <c r="G101" s="2">
+      <c r="H101" s="2">
         <f t="shared" si="5"/>
         <v>1704.8138294215264</v>
       </c>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A102">
         <v>100</v>
       </c>
-      <c r="B102">
+      <c r="B102" s="2">
         <f t="shared" si="4"/>
         <v>2704.813829421525</v>
       </c>
-      <c r="E102" s="2">
+      <c r="F102" s="3">
         <v>100</v>
       </c>
-      <c r="F102" s="2">
-        <f t="shared" ref="F102:F122" si="8">F101+G101+$D$2</f>
+      <c r="G102" s="2">
+        <f t="shared" ref="G102:G122" si="8">G101+H101+$E$2</f>
         <v>173186.19677157418</v>
       </c>
-      <c r="G102" s="2">
+      <c r="H102" s="2">
         <f t="shared" si="5"/>
         <v>1731.8619677157419</v>
       </c>
     </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A103">
         <v>101</v>
       </c>
-      <c r="B103">
+      <c r="B103" s="2">
         <f t="shared" si="4"/>
         <v>2731.8619677157403</v>
       </c>
-      <c r="E103" s="2">
+      <c r="F103" s="3">
         <v>101</v>
       </c>
-      <c r="F103" s="2">
+      <c r="G103" s="2">
         <f t="shared" si="8"/>
         <v>175918.05873928993</v>
       </c>
-      <c r="G103" s="2">
+      <c r="H103" s="2">
         <f t="shared" si="5"/>
         <v>1759.1805873928993</v>
       </c>
     </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A104">
         <v>102</v>
       </c>
-      <c r="B104">
+      <c r="B104" s="2">
         <f t="shared" si="4"/>
         <v>2759.1805873928979</v>
       </c>
-      <c r="E104" s="2">
+      <c r="F104" s="3">
         <v>102</v>
       </c>
-      <c r="F104" s="2">
+      <c r="G104" s="2">
         <f t="shared" si="8"/>
         <v>178677.23932668284</v>
       </c>
-      <c r="G104" s="2">
+      <c r="H104" s="2">
         <f t="shared" si="5"/>
         <v>1786.7723932668284</v>
       </c>
     </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A105">
         <v>103</v>
       </c>
-      <c r="B105">
+      <c r="B105" s="2">
         <f t="shared" si="4"/>
         <v>2786.7723932668268</v>
       </c>
-      <c r="E105" s="2">
+      <c r="F105" s="3">
         <v>103</v>
       </c>
-      <c r="F105" s="2">
+      <c r="G105" s="2">
         <f t="shared" si="8"/>
         <v>181464.01171994966</v>
       </c>
-      <c r="G105" s="2">
+      <c r="H105" s="2">
         <f t="shared" si="5"/>
         <v>1814.6401171994967</v>
       </c>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A106">
         <v>104</v>
       </c>
-      <c r="B106">
+      <c r="B106" s="2">
         <f t="shared" si="4"/>
         <v>2814.6401171994953</v>
       </c>
-      <c r="E106" s="2">
+      <c r="F106" s="3">
         <v>104</v>
       </c>
-      <c r="F106" s="2">
+      <c r="G106" s="2">
         <f t="shared" si="8"/>
         <v>184278.65183714917</v>
       </c>
-      <c r="G106" s="2">
+      <c r="H106" s="2">
         <f t="shared" si="5"/>
         <v>1842.7865183714916</v>
       </c>
     </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A107">
         <v>105</v>
       </c>
-      <c r="B107">
+      <c r="B107" s="2">
         <f t="shared" si="4"/>
         <v>2842.7865183714903</v>
       </c>
-      <c r="E107" s="2">
+      <c r="F107" s="3">
         <v>105</v>
       </c>
-      <c r="F107" s="2">
+      <c r="G107" s="2">
         <f t="shared" si="8"/>
         <v>187121.43835552066</v>
       </c>
-      <c r="G107" s="2">
+      <c r="H107" s="2">
         <f t="shared" si="5"/>
         <v>1871.2143835552067</v>
       </c>
     </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A108">
         <v>106</v>
       </c>
-      <c r="B108">
+      <c r="B108" s="2">
         <f t="shared" si="4"/>
         <v>2871.2143835552051</v>
       </c>
-      <c r="E108" s="2">
+      <c r="F108" s="3">
         <v>106</v>
       </c>
-      <c r="F108" s="2">
+      <c r="G108" s="2">
         <f t="shared" si="8"/>
         <v>189992.65273907586</v>
       </c>
-      <c r="G108" s="2">
+      <c r="H108" s="2">
         <f t="shared" si="5"/>
         <v>1899.9265273907586</v>
       </c>
     </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A109">
         <v>107</v>
       </c>
-      <c r="B109">
+      <c r="B109" s="2">
         <f t="shared" si="4"/>
         <v>2899.9265273907572</v>
       </c>
-      <c r="E109" s="2">
+      <c r="F109" s="3">
         <v>107</v>
       </c>
-      <c r="F109" s="2">
+      <c r="G109" s="2">
         <f t="shared" si="8"/>
         <v>192892.57926646661</v>
       </c>
-      <c r="G109" s="2">
+      <c r="H109" s="2">
         <f t="shared" si="5"/>
         <v>1928.925792664666</v>
       </c>
     </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A110">
         <v>108</v>
       </c>
-      <c r="B110">
+      <c r="B110" s="2">
         <f t="shared" si="4"/>
         <v>2928.9257926646646</v>
       </c>
-      <c r="E110" s="2">
+      <c r="F110" s="3">
         <v>108</v>
       </c>
-      <c r="F110" s="2">
+      <c r="G110" s="2">
         <f t="shared" si="8"/>
         <v>195821.50505913128</v>
       </c>
-      <c r="G110" s="2">
+      <c r="H110" s="2">
         <f t="shared" si="5"/>
         <v>1958.2150505913128</v>
       </c>
     </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A111">
         <v>109</v>
       </c>
-      <c r="B111">
+      <c r="B111" s="2">
         <f t="shared" si="4"/>
         <v>2958.2150505913114</v>
       </c>
-      <c r="E111" s="2">
+      <c r="F111" s="3">
         <v>109</v>
       </c>
-      <c r="F111" s="2">
+      <c r="G111" s="2">
         <f t="shared" si="8"/>
         <v>198779.72010972258</v>
       </c>
-      <c r="G111" s="2">
+      <c r="H111" s="2">
         <f t="shared" si="5"/>
         <v>1987.7972010972258</v>
       </c>
     </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A112">
         <v>110</v>
       </c>
-      <c r="B112">
+      <c r="B112" s="2">
         <f t="shared" si="4"/>
         <v>2987.7972010972244</v>
       </c>
-      <c r="E112" s="2">
+      <c r="F112" s="3">
         <v>110</v>
       </c>
-      <c r="F112" s="2">
+      <c r="G112" s="2">
         <f t="shared" si="8"/>
         <v>201767.51731081979</v>
       </c>
-      <c r="G112" s="2">
+      <c r="H112" s="2">
         <f t="shared" si="5"/>
         <v>2017.6751731081979</v>
       </c>
     </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A113">
         <v>111</v>
       </c>
-      <c r="B113">
+      <c r="B113" s="2">
         <f t="shared" si="4"/>
         <v>3017.6751731081968</v>
       </c>
-      <c r="E113" s="2">
+      <c r="F113" s="3">
         <v>111</v>
       </c>
-      <c r="F113" s="2">
+      <c r="G113" s="2">
         <f t="shared" si="8"/>
         <v>204785.192483928</v>
       </c>
-      <c r="G113" s="2">
+      <c r="H113" s="2">
         <f t="shared" si="5"/>
         <v>2047.8519248392799</v>
       </c>
     </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A114">
         <v>112</v>
       </c>
-      <c r="B114">
+      <c r="B114" s="2">
         <f t="shared" si="4"/>
         <v>3047.8519248392786</v>
       </c>
-      <c r="E114" s="2">
+      <c r="F114" s="3">
         <v>112</v>
       </c>
-      <c r="F114" s="2">
+      <c r="G114" s="2">
         <f t="shared" si="8"/>
         <v>207833.04440876728</v>
       </c>
-      <c r="G114" s="2">
+      <c r="H114" s="2">
         <f t="shared" si="5"/>
         <v>2078.3304440876727</v>
       </c>
     </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A115">
         <v>113</v>
       </c>
-      <c r="B115">
+      <c r="B115" s="2">
         <f t="shared" si="4"/>
         <v>3078.3304440876714</v>
       </c>
-      <c r="E115" s="2">
+      <c r="F115" s="3">
         <v>113</v>
       </c>
-      <c r="F115" s="2">
+      <c r="G115" s="2">
         <f t="shared" si="8"/>
         <v>210911.37485285496</v>
       </c>
-      <c r="G115" s="2">
+      <c r="H115" s="2">
         <f t="shared" si="5"/>
         <v>2109.1137485285499</v>
       </c>
     </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A116">
         <v>114</v>
       </c>
-      <c r="B116">
+      <c r="B116" s="2">
         <f t="shared" si="4"/>
         <v>3109.1137485285481</v>
       </c>
-      <c r="E116" s="2">
+      <c r="F116" s="3">
         <v>114</v>
       </c>
-      <c r="F116" s="2">
+      <c r="G116" s="2">
         <f t="shared" si="8"/>
         <v>214020.48860138352</v>
       </c>
-      <c r="G116" s="2">
+      <c r="H116" s="2">
         <f t="shared" si="5"/>
         <v>2140.2048860138352</v>
       </c>
     </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A117">
         <v>115</v>
       </c>
-      <c r="B117">
+      <c r="B117" s="2">
         <f t="shared" si="4"/>
         <v>3140.2048860138334</v>
       </c>
-      <c r="E117" s="2">
+      <c r="F117" s="3">
         <v>115</v>
       </c>
-      <c r="F117" s="2">
+      <c r="G117" s="2">
         <f t="shared" si="8"/>
         <v>217160.69348739737</v>
       </c>
-      <c r="G117" s="2">
+      <c r="H117" s="2">
         <f t="shared" si="5"/>
         <v>2171.6069348739738</v>
       </c>
     </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A118">
         <v>116</v>
       </c>
-      <c r="B118">
+      <c r="B118" s="2">
         <f t="shared" si="4"/>
         <v>3171.6069348739716</v>
       </c>
-      <c r="E118" s="2">
+      <c r="F118" s="3">
         <v>116</v>
       </c>
-      <c r="F118" s="2">
+      <c r="G118" s="2">
         <f t="shared" si="8"/>
         <v>220332.30042227134</v>
       </c>
-      <c r="G118" s="2">
+      <c r="H118" s="2">
         <f t="shared" si="5"/>
         <v>2203.3230042227133</v>
       </c>
     </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A119">
         <v>117</v>
       </c>
-      <c r="B119">
+      <c r="B119" s="2">
         <f t="shared" si="4"/>
         <v>3203.3230042227115</v>
       </c>
-      <c r="E119" s="2">
+      <c r="F119" s="3">
         <v>117</v>
       </c>
-      <c r="F119" s="2">
+      <c r="G119" s="2">
         <f t="shared" si="8"/>
         <v>223535.62342649404</v>
       </c>
-      <c r="G119" s="2">
+      <c r="H119" s="2">
         <f t="shared" si="5"/>
         <v>2235.3562342649407</v>
       </c>
     </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A120">
         <v>118</v>
       </c>
-      <c r="B120">
+      <c r="B120" s="2">
         <f t="shared" si="4"/>
         <v>3235.3562342649384</v>
       </c>
-      <c r="E120" s="2">
+      <c r="F120" s="3">
         <v>118</v>
       </c>
-      <c r="F120" s="2">
+      <c r="G120" s="2">
         <f t="shared" si="8"/>
         <v>226770.97966075898</v>
       </c>
-      <c r="G120" s="2">
+      <c r="H120" s="2">
         <f t="shared" si="5"/>
         <v>2267.7097966075899</v>
       </c>
     </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A121">
         <v>119</v>
       </c>
-      <c r="B121">
+      <c r="B121" s="2">
         <f t="shared" si="4"/>
         <v>3267.7097966075876</v>
       </c>
-      <c r="E121" s="2">
+      <c r="F121" s="3">
         <v>119</v>
       </c>
-      <c r="F121" s="2">
+      <c r="G121" s="2">
         <f t="shared" si="8"/>
         <v>230038.68945736656</v>
       </c>
-      <c r="G121" s="2">
+      <c r="H121" s="2">
         <f t="shared" si="5"/>
         <v>2300.3868945736658</v>
       </c>
     </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A122">
         <v>120</v>
       </c>
-      <c r="B122">
+      <c r="B122" s="2">
         <f t="shared" si="4"/>
         <v>3300.3868945736635</v>
       </c>
-      <c r="E122" s="2">
+      <c r="F122" s="3">
         <v>120</v>
       </c>
-      <c r="F122" s="2">
+      <c r="G122" s="2">
         <f t="shared" si="8"/>
         <v>233339.07635194022</v>
       </c>
-      <c r="G122" s="2">
+      <c r="H122" s="2">
         <f t="shared" si="5"/>
         <v>2333.3907635194023</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="F1:H1"/>
+  </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>